--- a/artfynd/A 45535-2023 artfynd.xlsx
+++ b/artfynd/A 45535-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45535-2023 artfynd.xlsx
+++ b/artfynd/A 45535-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97670563</v>
+        <v>113049128</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
+        <v>56910</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,57 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kolvik, Srm</t>
+          <t>Kolviksbergen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568336.6089083293</v>
+        <v>568463</v>
       </c>
       <c r="R2" t="n">
-        <v>6567392.108289131</v>
+        <v>6567244</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +761,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1980-05-16</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1980-05-16</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett par talltitor varnade tillsammans med tofsmes. I avverkningsanmäld kontinuitetsskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,28 +792,23 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>sjöstrand</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113036418</v>
+        <v>113048818</v>
       </c>
       <c r="B3" t="n">
         <v>97314</v>
@@ -827,7 +843,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,14 +856,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kolviksberget, Kolvik, Srm</t>
+          <t>Kolviksbergen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568445</v>
+        <v>568454</v>
       </c>
       <c r="R3" t="n">
-        <v>6567530</v>
+        <v>6567249</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,27 +890,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Troligen fler plantor som gömmer sig i mossan. Växer i kontinuitetsskog med gran som sluttar ner mot Hjälmaren i västlig riktning.</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,19 +914,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Fuktig barrblandskog. Kontinuitetsskog med gamla granar och enstaka tallar.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -932,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113049128</v>
+        <v>113048379</v>
       </c>
       <c r="B4" t="n">
-        <v>56910</v>
+        <v>97314</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,43 +944,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -988,13 +984,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568463</v>
+        <v>568316</v>
       </c>
       <c r="R4" t="n">
-        <v>6567244</v>
+        <v>6567233</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1023,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1033,12 +1029,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ett par talltitor varnade tillsammans med tofsmes. I avverkningsanmäld kontinuitetsskog</t>
+          <t>15 plantor som växer under en gammal tall i avverkningsanmäld kontinuitetsskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,7 +1061,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113048818</v>
+        <v>113052263</v>
       </c>
       <c r="B5" t="n">
         <v>97314</v>
@@ -1100,7 +1096,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1113,14 +1109,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kolviksbergen, Srm</t>
+          <t>Kolviksbergen, Kolvik, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568454</v>
+        <v>568467</v>
       </c>
       <c r="R5" t="n">
-        <v>6567249</v>
+        <v>6567374</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1152,7 +1148,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1162,7 +1158,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer i blåbärsriset under senvuxen gran i sluttning ner mot Hjälmaren.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,8 +1172,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog på hällmark. Kontinuitetsskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1189,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113048379</v>
+        <v>113050136</v>
       </c>
       <c r="B6" t="n">
-        <v>97314</v>
+        <v>97326</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,14 +1236,10 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1241,13 +1249,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568316</v>
+        <v>568488</v>
       </c>
       <c r="R6" t="n">
-        <v>6567233</v>
+        <v>6567389</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1276,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1286,12 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>15 plantor som växer under en gammal tall i avverkningsanmäld kontinuitetsskog</t>
+          <t>Växer i sluttning i västlig riktning mot Hjälmaren. Kontinuitetsskog som är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113052263</v>
+        <v>113119048</v>
       </c>
       <c r="B7" t="n">
-        <v>97314</v>
+        <v>97650</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1353,30 +1361,26 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kolviksbergen, Kolvik, Srm</t>
+          <t>Kolviksbergen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568467</v>
+        <v>568342</v>
       </c>
       <c r="R7" t="n">
-        <v>6567374</v>
+        <v>6567293</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1400,27 +1404,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växer i blåbärsriset under senvuxen gran i sluttning ner mot Hjälmaren.</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1429,19 +1428,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrblandskog på hällmark. Kontinuitetsskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1458,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113050136</v>
+        <v>113120519</v>
       </c>
       <c r="B8" t="n">
-        <v>97326</v>
+        <v>97650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1491,11 +1479,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1506,13 +1490,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568488</v>
+        <v>568470</v>
       </c>
       <c r="R8" t="n">
-        <v>6567389</v>
+        <v>6567430</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1536,27 +1520,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer i sluttning i västlig riktning mot Hjälmaren. Kontinuitetsskog som är avverkningsanmäld.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1583,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113121047</v>
+        <v>113118040</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
+        <v>57284</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1595,53 +1574,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kolvik, Srm</t>
+          <t>Kolviksbergen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568425</v>
+        <v>568342</v>
       </c>
       <c r="R9" t="n">
-        <v>6567521</v>
+        <v>6567292</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1670,7 +1649,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1680,12 +1659,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Friska plantor i sluttning ner mot Hjälmaren. Gammal granskog med hög fuktighet. Kontinuitetsskog</t>
+          <t>Födosökande i kontinuitetsskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1712,7 +1691,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113121503</v>
+        <v>113120182</v>
       </c>
       <c r="B10" t="n">
         <v>97650</v>
@@ -1747,7 +1726,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1764,13 +1743,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568423</v>
+        <v>568420</v>
       </c>
       <c r="R10" t="n">
-        <v>6567511</v>
+        <v>6567172</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1799,7 +1778,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1809,12 +1788,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växer i mossan vid rötterna av en gran. Kontinuitetsskog</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1841,7 +1815,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113119048</v>
+        <v>113119893</v>
       </c>
       <c r="B11" t="n">
         <v>97650</v>
@@ -1874,28 +1848,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kolviksbergen, Srm</t>
+          <t>Kolvik, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568342</v>
+        <v>568369</v>
       </c>
       <c r="R11" t="n">
-        <v>6567293</v>
+        <v>6567289</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1924,7 +1898,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1934,7 +1908,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1961,7 +1935,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113120519</v>
+        <v>113132601</v>
       </c>
       <c r="B12" t="n">
         <v>97650</v>
@@ -1994,21 +1968,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kolviksbergen, Srm</t>
+          <t>Kolvik, Kolvik, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568470</v>
+        <v>568401</v>
       </c>
       <c r="R12" t="n">
-        <v>6567430</v>
+        <v>6567247</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2035,22 +2017,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2059,8 +2041,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrblandskog. Kontinuitetsskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2074,767 +2067,6 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>113118040</v>
-      </c>
-      <c r="B13" t="n">
-        <v>57284</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>102977</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Gröngöling</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Picus viridis</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Kolviksbergen, Srm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>568342</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6567292</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Näshulta</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2023-11-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2023-11-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födosökande i kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>113120182</v>
-      </c>
-      <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Kolvik, Srm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>568420</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6567172</v>
-      </c>
-      <c r="S14" t="n">
-        <v>6</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Näshulta</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2023-11-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2023-11-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>113121569</v>
-      </c>
-      <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Kolvik, Srm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>568391</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6567478</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Näshulta</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2023-11-06</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2023-11-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>113121340</v>
-      </c>
-      <c r="B16" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Kolvik, Srm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>568427</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6567553</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Näshulta</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2023-11-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2023-11-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Växer på undersidan av grov granlåga. Kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>113121838</v>
-      </c>
-      <c r="B17" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Kolvik, Srm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>568382</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6567460</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Näshulta</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2023-11-06</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2023-11-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>113132601</v>
-      </c>
-      <c r="B18" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Kolvik, Kolvik, Srm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>568401</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6567247</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Näshulta</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2023-11-02</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2023-11-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Barrblandskog. Kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45535-2023 artfynd.xlsx
+++ b/artfynd/A 45535-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113049128</v>
+        <v>113122149</v>
       </c>
       <c r="B2" t="n">
-        <v>56910</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,53 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kolviksbergen, Srm</t>
+          <t>Kolvik, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568463</v>
+        <v>568366</v>
       </c>
       <c r="R2" t="n">
-        <v>6567244</v>
+        <v>6567337</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,27 +747,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ett par talltitor varnade tillsammans med tofsmes. I avverkningsanmäld kontinuitetsskog</t>
+          <t>Växer på knotig gammeltall. Kontinuitetsskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -808,51 +794,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113048818</v>
+        <v>113118040</v>
       </c>
       <c r="B3" t="n">
-        <v>97314</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -860,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568454</v>
+        <v>568342</v>
       </c>
       <c r="R3" t="n">
-        <v>6567249</v>
+        <v>6567292</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,22 +871,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökande i kontinuitetsskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,51 +918,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113048379</v>
+        <v>113049128</v>
       </c>
       <c r="B4" t="n">
-        <v>97314</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -984,13 +969,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568316</v>
+        <v>568463</v>
       </c>
       <c r="R4" t="n">
-        <v>6567233</v>
+        <v>6567243</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1019,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,12 +1014,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>15 plantor som växer under en gammal tall i avverkningsanmäld kontinuitetsskog</t>
+          <t>Ett par talltitor varnade tillsammans med tofsmes. I avverkningsanmäld kontinuitetsskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,15 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113052263</v>
+        <v>113048155</v>
       </c>
       <c r="B5" t="n">
-        <v>97314</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1076,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1109,17 +1089,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kolviksbergen, Kolvik, Srm</t>
+          <t>Kolvik, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568467</v>
+        <v>568398</v>
       </c>
       <c r="R5" t="n">
-        <v>6567374</v>
+        <v>6567310</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1148,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1158,12 +1138,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växer i blåbärsriset under senvuxen gran i sluttning ner mot Hjälmaren.</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,19 +1147,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrblandskog på hällmark. Kontinuitetsskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1201,15 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113050136</v>
+        <v>113048379</v>
       </c>
       <c r="B6" t="n">
-        <v>97326</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,10 +1195,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1249,13 +1212,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568488</v>
+        <v>568316</v>
       </c>
       <c r="R6" t="n">
-        <v>6567389</v>
+        <v>6567233</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1284,7 +1247,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1257,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växer i sluttning i västlig riktning mot Hjälmaren. Kontinuitetsskog som är avverkningsanmäld.</t>
+          <t>15 plantor som växer under en gammal tall i avverkningsanmäld kontinuitetsskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1326,15 +1289,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113119048</v>
+        <v>113048818</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,10 +1319,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1374,13 +1336,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568342</v>
+        <v>568454</v>
       </c>
       <c r="R7" t="n">
-        <v>6567293</v>
+        <v>6567249</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1404,22 +1366,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1446,15 +1408,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113120519</v>
+        <v>113050136</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1436,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1490,13 +1451,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568470</v>
+        <v>568488</v>
       </c>
       <c r="R8" t="n">
-        <v>6567430</v>
+        <v>6567389</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1520,22 +1481,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer i sluttning i västlig riktning mot Hjälmaren. Kontinuitetsskog som är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1562,65 +1528,60 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113118040</v>
+        <v>113052263</v>
       </c>
       <c r="B9" t="n">
-        <v>57284</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kolviksbergen, Srm</t>
+          <t>Kolviksbergen, Kolvik, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568342</v>
+        <v>568467</v>
       </c>
       <c r="R9" t="n">
-        <v>6567292</v>
+        <v>6567374</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1644,27 +1605,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Födosökande i kontinuitetsskog</t>
+          <t>Växer i blåbärsriset under senvuxen gran i sluttning ner mot Hjälmaren.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,8 +1634,19 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrblandskog på hällmark. Kontinuitetsskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1691,15 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113120182</v>
+        <v>113119048</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,27 +1693,23 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kolvik, Srm</t>
+          <t>Kolviksbergen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568420</v>
+        <v>568342</v>
       </c>
       <c r="R10" t="n">
-        <v>6567172</v>
+        <v>6567293</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1778,7 +1741,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1788,7 +1751,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1818,12 +1781,7 @@
         <v>113119893</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,15 +1893,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113132601</v>
+        <v>113120182</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1923,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1983,17 +1936,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kolvik, Kolvik, Srm</t>
+          <t>Kolvik, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568401</v>
+        <v>568420</v>
       </c>
       <c r="R12" t="n">
-        <v>6567247</v>
+        <v>6567172</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2017,22 +1970,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2041,19 +1994,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Barrblandskog. Kontinuitetsskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2067,6 +2009,371 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113120519</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kolviksbergen, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>568470</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6567430</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-11-06</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-11-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113122116</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kolvik, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>568380</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6567352</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-11-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-11-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växer i fuktig sänka i hällmarken. Kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>113132601</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kolvik, Kolvik, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>568401</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6567247</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Barrblandskog. Kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45535-2023 artfynd.xlsx
+++ b/artfynd/A 45535-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113122149</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113118040</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,6 +1058,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113049128</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1162,6 +1182,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113048155</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1286,6 +1311,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113048379</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1405,6 +1435,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113048818</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1525,6 +1560,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113050136</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1660,6 +1700,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113052263</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1775,6 +1820,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113119048</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1890,6 +1940,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113119893</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2009,6 +2064,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120182</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2120,6 +2180,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120519</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2244,6 +2309,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113122116</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2374,8 +2444,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113132601</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>